--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N126_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N126_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.05999777454537</v>
+        <v>5.209749638363622</v>
       </c>
       <c r="D2" t="n">
-        <v>34.21346335724182</v>
+        <v>5.559687795551796</v>
       </c>
       <c r="E2" t="n">
-        <v>8.995143610264986</v>
+        <v>1.46171083666806</v>
       </c>
       <c r="F2" t="n">
-        <v>5.658080677378257</v>
+        <v>0.9194381100739666</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.96052042740443</v>
+        <v>6.16858456945322</v>
       </c>
       <c r="D3" t="n">
-        <v>39.72783740591564</v>
+        <v>6.455773578461292</v>
       </c>
       <c r="E3" t="n">
-        <v>8.995143610264986</v>
+        <v>1.46171083666806</v>
       </c>
       <c r="F3" t="n">
-        <v>5.658080677378257</v>
+        <v>0.9194381100739666</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.97842024397662</v>
+        <v>7.633993289646201</v>
       </c>
       <c r="D4" t="n">
-        <v>41.76311554562863</v>
+        <v>6.786506276164652</v>
       </c>
       <c r="E4" t="n">
-        <v>8.995143610264986</v>
+        <v>1.46171083666806</v>
       </c>
       <c r="F4" t="n">
-        <v>5.658080677378257</v>
+        <v>0.9194381100739666</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.77101786353685</v>
+        <v>9.062790402824739</v>
       </c>
       <c r="D5" t="n">
-        <v>48.892326324336</v>
+        <v>7.9450030277046</v>
       </c>
       <c r="E5" t="n">
-        <v>8.995143610264986</v>
+        <v>1.46171083666806</v>
       </c>
       <c r="F5" t="n">
-        <v>5.658080677378257</v>
+        <v>0.9194381100739666</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.76204836957839</v>
+        <v>7.923832860056488</v>
       </c>
       <c r="D6" t="n">
-        <v>41.37263497195402</v>
+        <v>6.723053182942529</v>
       </c>
       <c r="E6" t="n">
-        <v>8.995143610264986</v>
+        <v>1.46171083666806</v>
       </c>
       <c r="F6" t="n">
-        <v>5.658080677378257</v>
+        <v>0.9194381100739666</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.11894817968307</v>
+        <v>9.2818290791985</v>
       </c>
       <c r="D7" t="n">
-        <v>51.08846228719246</v>
+        <v>8.301875121668774</v>
       </c>
       <c r="E7" t="n">
-        <v>8.995143610264986</v>
+        <v>1.46171083666806</v>
       </c>
       <c r="F7" t="n">
-        <v>5.658080677378257</v>
+        <v>0.9194381100739666</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
